--- a/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,95 +991,95 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Enable Create Notification</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KT60GDHD4D88JAT5V1KJ0PPT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT60GDHD4D88JAT5V1KJ0PPT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Enable Update Notification</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KT631S84NX86CTP525MTBK36</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT631S84NX86CTP525MTBK36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mapping Custom Attributes</t>
+          <t>Enable Deactivate Notification</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>h_01KT63ETFE6CNVK80GAQ80N2RE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT63ETFE6CNVK80GAQ80N2RE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,107 +1089,107 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Create Custom Attributes in Okta</t>
+          <t>Mapping Custom Attributes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Map Custom Attribute to Okta Profile</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+          <t>h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADP Workforce Now Worker Attributes</t>
+          <t>Filter Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01HXV5081PWKBEKH540JBRRMQM</t>
+          <t>h_01KT6DRJNZ7F25Q70W52ASYAH1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01HXV5081PWKBEKH540JBRRMQM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT6DRJNZ7F25Q70W52ASYAH1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Run Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Troubleshooting</t>
+          <t>Create Custom Attributes in Okta</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,32 +1199,120 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KFFVZ8N3N820WBEPX37HT843</t>
+          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KFFVZ8N3N820WBEPX37HT843</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Map Custom Attribute to Okta Profile</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ADP Workforce Now Worker Attributes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01HXV5081PWKBEKH540JBRRMQM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01HXV5081PWKBEKH540JBRRMQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Run Integration</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Troubleshooting</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KFFVZ8N3N820WBEPX37HT843</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KFFVZ8N3N820WBEPX37HT843</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>FAQs</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>h_01KADNT38N98M887JSH86ZKKVY</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KADNT38N98M887JSH86ZKKVY</t>
         </is>

--- a/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,51 +837,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Okta Deletions</t>
+          <t>Onboarding Date Offset</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KAFZEEN74H2QQ46MSHRP1JWT</t>
+          <t>h_01KVDB8Z48217HCEZNPZGJ3R2M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#01KAFZEEN74H2QQ46MSHRP1JWT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDB8Z48217HCEZNPZGJ3R2M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unique Identity</t>
+          <t>Offboarding Date Offset</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K5VEHZF56V5FCKR8PQ1NN7TQ</t>
+          <t>h_01KVDB9N8SENSHK7E417R5EN7M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K5VEHZF56V5FCKR8PQ1NN7TQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDB9N8SENSHK7E417R5EN7M</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Okta Deletions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>01KAFZEEN74H2QQ46MSHRP1JWT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#01KAFZEEN74H2QQ46MSHRP1JWT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K5VEHZF56V5FCKR8PQ1NN7TQ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K5VEHZF56V5FCKR8PQ1NN7TQ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Monitored provisioning Notification</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KEH0NNX6H4M85JXE0FX4J916</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KEH0NNX6H4M85JXE0FX4J916</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enable Create Notification</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KT60GDHD4D88JAT5V1KJ0PPT</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT60GDHD4D88JAT5V1KJ0PPT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enable Update Notification</t>
+          <t>Integration Completed Notification</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,129 +1023,129 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KT631S84NX86CTP525MTBK36</t>
+          <t>h_01KVDBQXVBZ5VNDJAMEHC5ECHY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT631S84NX86CTP525MTBK36</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDBQXVBZ5VNDJAMEHC5ECHY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enable Deactivate Notification</t>
+          <t>Report Settings for Email Attachment</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KT63ETFE6CNVK80GAQ80N2RE</t>
+          <t>h_01KVDBTZ0NKFC2EQWKX1NFJ4AA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT63ETFE6CNVK80GAQ80N2RE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDBTZ0NKFC2EQWKX1NFJ4AA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Report Detail Level : Select the report detail level from the dropdown menu. The following are the available options:</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KVDBV1HQEJJDZB3ZVN7P5SXQ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDBV1HQEJJDZB3ZVN7P5SXQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Full Details : All attribute details are displayed.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KVDBXH8079SQND3PX04VCG4Q</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDBXH8079SQND3PX04VCG4Q</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mapping Custom Attributes</t>
+          <t>Custom : Includes or excludes selected attributes. The following parameters are displayed once you select Custom :</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>h_01KVDBVYWYYP19E6RTMWE0QE33</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDBVYWYYP19E6RTMWE0QE33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Monitored provisioning Notification</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
+          <t>h_01KEH0NNX6H4M85JXE0FX4J916</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KEH0NNX6H4M85JXE0FX4J916</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Filter Settings</t>
+          <t>Enable Create Notification</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,85 +1155,85 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KT6DRJNZ7F25Q70W52ASYAH1</t>
+          <t>h_01KT60GDHD4D88JAT5V1KJ0PPT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT6DRJNZ7F25Q70W52ASYAH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT60GDHD4D88JAT5V1KJ0PPT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Enable Update Notification</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KT631S84NX86CTP525MTBK36</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT631S84NX86CTP525MTBK36</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Create Custom Attributes in Okta</t>
+          <t>Enable Deactivate Notification</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+          <t>h_01KT63ETFE6CNVK80GAQ80N2RE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT63ETFE6CNVK80GAQ80N2RE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Map Custom Attribute to Okta Profile</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADP Workforce Now Worker Attributes</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,76 +1243,274 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01HXV5081PWKBEKH540JBRRMQM</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01HXV5081PWKBEKH540JBRRMQM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Run Integration</t>
+          <t>Worker Map</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Troubleshooting</t>
+          <t>Candidate Map</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KFFVZ8N3N820WBEPX37HT843</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KFFVZ8N3N820WBEPX37HT843</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Mapping Custom Attributes</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Group Rules</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Filter Settings</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KT6DRJNZ7F25Q70W52ASYAH1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KT6DRJNZ7F25Q70W52ASYAH1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Create Custom Attributes in Okta</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Map Custom Attribute to Okta Profile</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ADP Workforce Now Worker Attributes</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01HXV5081PWKBEKH540JBRRMQM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01HXV5081PWKBEKH540JBRRMQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Run Integration</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Troubleshooting</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KFFVZ8N3N820WBEPX37HT843</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KFFVZ8N3N820WBEPX37HT843</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>FAQs</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>h_01KADNT38N98M887JSH86ZKKVY</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KADNT38N98M887JSH86ZKKVY</t>
         </is>

--- a/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Okta-Integration-Guide/headings.xlsx
@@ -1089,12 +1089,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KVDBXH8079SQND3PX04VCG4Q</t>
+          <t>h_01KWEFHX61G7VNKCHV6MZ9S2YS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KVDBXH8079SQND3PX04VCG4Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Okta-Integration-Guide/#h_01KWEFHX61G7VNKCHV6MZ9S2YS</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enable Create Notification</t>
+          <t>New User Notification</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enable Update Notification</t>
+          <t>User Update Notification</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enable Deactivate Notification</t>
+          <t>User Deactivate Notification</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
